--- a/Дело3а-78-2026Таганай/02_Отчёты/02.2_Обоснование_2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/02_Отчёты/02.2_Обоснование_2025/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92537297823</v>
+        <v>46157.9311073741</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/02_Отчёты/02.2_Обоснование_2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/02_Отчёты/02.2_Обоснование_2025/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9311073741</v>
+        <v>46157.93365955921</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/02_Отчёты/02.2_Обоснование_2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/02_Отчёты/02.2_Обоснование_2025/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93365955921</v>
+        <v>46157.93668139003</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/02_Отчёты/02.2_Обоснование_2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/02_Отчёты/02.2_Обоснование_2025/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93668139003</v>
+        <v>46158.28192525049</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/02_Отчёты/02.2_Обоснование_2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/02_Отчёты/02.2_Обоснование_2025/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28192525049</v>
+        <v>46158.29713788858</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/02_Отчёты/02.2_Обоснование_2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/02_Отчёты/02.2_Обоснование_2025/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29713788858</v>
+        <v>46158.29787924994</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/02_Отчёты/02.2_Обоснование_2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/02_Отчёты/02.2_Обоснование_2025/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29787924994</v>
+        <v>46158.33354028795</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/02_Отчёты/02.2_Обоснование_2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/02_Отчёты/02.2_Обоснование_2025/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33354028795</v>
+        <v>46158.3720961049</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/02_Отчёты/02.2_Обоснование_2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/02_Отчёты/02.2_Обоснование_2025/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.3720961049</v>
+        <v>46158.37428907095</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
